--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_08-07-2026.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_08-07-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Recticel_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F881F9B-7821-4F8E-A561-02665DFFD5F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53FEE34D-6072-4C61-81B7-6E01FD598962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6480" yWindow="945" windowWidth="21600" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34965" yWindow="405" windowWidth="21600" windowHeight="12750" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="450" uniqueCount="264">
   <si>
     <t>SKU</t>
   </si>
@@ -809,6 +809,9 @@
   </si>
   <si>
     <t>£58.88</t>
+  </si>
+  <si>
+    <t>£276.59</t>
   </si>
 </sst>
 </file>
@@ -2078,7 +2081,7 @@
         <v>186</v>
       </c>
       <c r="C17" t="s">
-        <v>23</v>
+        <v>263</v>
       </c>
       <c r="D17" t="s">
         <v>23</v>
